--- a/public/static/产品导入模板.xlsx
+++ b/public/static/产品导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="产品导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>序号</t>
   </si>
@@ -37,7 +37,7 @@
   </si>
   <si>
     <r>
-      <t>规格型号</t>
+      <t>品名规格</t>
     </r>
     <r>
       <rPr>
@@ -55,6 +55,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>主单位</t>
     </r>
     <r>
@@ -160,6 +167,50 @@
     <t>品牌</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否销售</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否贸易件</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -169,7 +220,10 @@
     <t>乘</t>
   </si>
   <si>
-    <t>自制</t>
+    <t>组装</t>
+  </si>
+  <si>
+    <t>是</t>
   </si>
   <si>
     <t>产品编码：需根据编码规则设置中，如果是自动生成，则无需填写，如果是手动输入，则必须输入</t>
@@ -1188,7 +1242,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1438,21 +1492,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:M48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
     <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.2222222222222" customWidth="1"/>
-    <col min="8" max="10" width="16.4444444444444" customWidth="1"/>
-    <col min="11" max="11" width="19.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="17.225" customWidth="1"/>
+    <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
+    <col min="11" max="13" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:11">
+    <row r="1" ht="25" customHeight="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1483,13 +1537,19 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:11">
+    <row r="2" ht="20" customHeight="1" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1498,13 +1558,19 @@
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" s="7"/>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1553,12 +1619,15 @@
     <row r="47" ht="20" customHeight="1"/>
     <row r="48" ht="20" customHeight="1"/>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"乘,除"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
-      <formula1>"自制,采购,外协"</formula1>
+      <formula1>"组装,生产,采购,外协"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 L2">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1570,34 +1639,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A27"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1"/>

--- a/public/static/产品导入模板.xlsx
+++ b/public/static/产品导入模板.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>序号</t>
   </si>
@@ -216,6 +216,9 @@
       </rPr>
       <t>(必填)</t>
     </r>
+  </si>
+  <si>
+    <t>工艺路线</t>
   </si>
   <si>
     <t>备注</t>
@@ -1496,7 +1499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
@@ -1508,9 +1511,10 @@
     <col min="7" max="7" width="17.225" customWidth="1"/>
     <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
     <col min="11" max="13" width="19.4416666666667" customWidth="1"/>
+    <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:13">
+    <row r="1" ht="25" customHeight="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1550,10 +1554,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
+    <row r="2" ht="20" customHeight="1" spans="1:14">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1562,17 +1569,18 @@
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1628,7 +1636,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>"组装,生产,采购,外协"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 L2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:L2">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1648,27 +1656,27 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1"/>

--- a/public/static/产品导入模板.xlsx
+++ b/public/static/产品导入模板.xlsx
@@ -28,9 +28,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>序号</t>
+  </si>
+  <si>
+    <r>
+      <t>产品分类</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <t>产品编码</t>
@@ -1499,22 +1514,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
     <col min="2" max="2" width="18.225" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.225" customWidth="1"/>
-    <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
-    <col min="11" max="13" width="19.4416666666667" customWidth="1"/>
-    <col min="14" max="14" width="20.5" customWidth="1"/>
+    <col min="3" max="4" width="23.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.225" customWidth="1"/>
+    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.225" customWidth="1"/>
+    <col min="9" max="11" width="16.4416666666667" customWidth="1"/>
+    <col min="12" max="14" width="19.4416666666667" customWidth="1"/>
+    <col min="15" max="15" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:14">
+    <row r="1" ht="25" customHeight="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1551,36 +1566,40 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:14">
+    <row r="2" ht="20" customHeight="1" spans="1:15">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J2" s="7"/>
-      <c r="K2" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="K2" s="7"/>
       <c r="L2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1630,13 +1649,13 @@
     <row r="48" ht="20" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>"乘,除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2">
       <formula1>"组装,生产,采购,外协"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:L2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:M2">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1656,27 +1675,27 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1"/>

--- a/public/static/产品导入模板.xlsx
+++ b/public/static/产品导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="产品导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>序号</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>导入系统中的产品，默认都是启用状态，创建时间默认当前时间，创建人默认当前导入人。</t>
+  </si>
+  <si>
+    <t>产品分类：填写产品分类编码</t>
+  </si>
+  <si>
+    <t>工艺路线：填写工艺路线编码</t>
   </si>
 </sst>
 </file>
@@ -1698,8 +1704,16 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1"/>
-    <row r="7" ht="28" customHeight="1"/>
+    <row r="6" ht="28" customHeight="1" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="8" ht="28" customHeight="1"/>
     <row r="9" ht="28" customHeight="1"/>
     <row r="10" ht="28" customHeight="1"/>
